--- a/docs/case_files/CASE_TRIA.xlsx
+++ b/docs/case_files/CASE_TRIA.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" style="10" min="1" max="1"/>
@@ -1073,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="10" min="1" max="1"/>
@@ -1133,6 +1133,11 @@
           <t>B-2 DIAGNOSTIC FLAGS (dump analysis)</t>
         </is>
       </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>SPOT-EXT (v2.1 amendment 19/08)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="40.05" customHeight="1" s="10">
       <c r="A2" s="4" t="inlineStr">
@@ -1385,6 +1390,16 @@
           <t>flag_knife_crowd (gLSR↑&amp;ret&lt;-3%)</t>
         </is>
       </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>vol_spot_ext_usd</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>spot_ext_venue</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1446,6 +1461,24 @@
       <c r="AD3" t="n">
         <v>0.7756211218210215</v>
       </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>29162.22</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -1454,6 +1487,14 @@
       <c r="AP3" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>853490.51</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -1526,6 +1567,24 @@
       <c r="AD4" t="n">
         <v>0.9088800217793288</v>
       </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>14306.66</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -1534,6 +1593,14 @@
       <c r="AP4" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>740745.47</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -1609,6 +1676,24 @@
       <c r="AD5" t="n">
         <v>0.8965050415260998</v>
       </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>37694.97</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -1617,6 +1702,14 @@
       <c r="AP5" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>1163413.65</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -1698,6 +1791,24 @@
       <c r="AD6" t="n">
         <v>0.8526391200114819</v>
       </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>46618.95</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -1706,6 +1817,14 @@
       <c r="AP6" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>1271072.07</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -1784,6 +1903,24 @@
       <c r="AC7" t="n">
         <v>1.2925</v>
       </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI7" t="n">
+        <v>9070.1</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -1792,6 +1929,14 @@
       <c r="AP7" t="inlineStr">
         <is>
           <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>524311.9399999999</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -1873,6 +2018,24 @@
       <c r="AC8" t="n">
         <v>1.3992</v>
       </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
+        <v>48855.26</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -1881,6 +2044,14 @@
       <c r="AP8" t="inlineStr">
         <is>
           <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>734785.84</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -1962,6 +2133,24 @@
       <c r="AC9" t="n">
         <v>1.6055</v>
       </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI9" t="n">
+        <v>8187.44</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -1970,6 +2159,14 @@
       <c r="AP9" t="inlineStr">
         <is>
           <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>330604.47</v>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2054,6 +2251,24 @@
       <c r="AD10" t="n">
         <v>0.8587</v>
       </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>24755.06</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2062,6 +2277,14 @@
       <c r="AP10" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>1015354.45</v>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2146,6 +2369,24 @@
       <c r="AD11" t="n">
         <v>0.9435</v>
       </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI11" t="n">
+        <v>10664.74</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2154,6 +2395,14 @@
       <c r="AP11" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>545209.3199999999</v>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2238,6 +2487,24 @@
       <c r="AD12" t="n">
         <v>0.8816000000000001</v>
       </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI12" t="n">
+        <v>6555.06</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2246,6 +2513,14 @@
       <c r="AP12" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>516101.93</v>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2330,6 +2605,24 @@
       <c r="AD13" t="n">
         <v>0.8622</v>
       </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI13" t="n">
+        <v>9744.65</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2338,6 +2631,14 @@
       <c r="AP13" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY13" t="n">
+        <v>637871.7</v>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2422,6 +2723,24 @@
       <c r="AD14" t="n">
         <v>0.8814</v>
       </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI14" t="n">
+        <v>12719.04</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2430,6 +2749,14 @@
       <c r="AP14" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY14" t="n">
+        <v>394994.32</v>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2514,6 +2841,24 @@
       <c r="AD15" t="n">
         <v>0.8945</v>
       </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI15" t="n">
+        <v>2972.5</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2522,6 +2867,14 @@
       <c r="AP15" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY15" t="n">
+        <v>142877.41</v>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2606,6 +2959,24 @@
       <c r="AD16" t="n">
         <v>1.0231</v>
       </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI16" t="n">
+        <v>12494.46</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2614,6 +2985,14 @@
       <c r="AP16" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY16" t="n">
+        <v>192112.53</v>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2698,6 +3077,24 @@
       <c r="AD17" t="n">
         <v>0.9944</v>
       </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI17" t="n">
+        <v>54079.04</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2706,6 +3103,14 @@
       <c r="AP17" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY17" t="n">
+        <v>415393.57</v>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2790,6 +3195,24 @@
       <c r="AD18" t="n">
         <v>0.9901</v>
       </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI18" t="n">
+        <v>11463.63</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2798,6 +3221,14 @@
       <c r="AP18" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY18" t="n">
+        <v>437112.13</v>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2882,6 +3313,24 @@
       <c r="AD19" t="n">
         <v>0.994</v>
       </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI19" t="n">
+        <v>20415.75</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2890,6 +3339,14 @@
       <c r="AP19" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY19" t="n">
+        <v>302106.41</v>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -2974,6 +3431,24 @@
       <c r="AD20" t="n">
         <v>0.9397</v>
       </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI20" t="n">
+        <v>26502.42</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -2982,6 +3457,14 @@
       <c r="AP20" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY20" t="n">
+        <v>401420.11</v>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3066,6 +3549,24 @@
       <c r="AD21" t="n">
         <v>0.9061</v>
       </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
+        <v>23424.27</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3074,6 +3575,14 @@
       <c r="AP21" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY21" t="n">
+        <v>315625.8</v>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3158,6 +3667,24 @@
       <c r="AD22" t="n">
         <v>0.8618</v>
       </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI22" t="n">
+        <v>146066.28</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3166,6 +3693,14 @@
       <c r="AP22" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY22" t="n">
+        <v>367900.28</v>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3250,6 +3785,24 @@
       <c r="AD23" t="n">
         <v>0.8088</v>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI23" t="n">
+        <v>24523.97</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3258,6 +3811,14 @@
       <c r="AP23" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY23" t="n">
+        <v>330277.46</v>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3342,6 +3903,24 @@
       <c r="AD24" t="n">
         <v>0.8575</v>
       </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI24" t="n">
+        <v>36079.69</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3350,6 +3929,14 @@
       <c r="AP24" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY24" t="n">
+        <v>576183.62</v>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3434,6 +4021,24 @@
       <c r="AD25" t="n">
         <v>0.8419</v>
       </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI25" t="n">
+        <v>10686.28</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3442,6 +4047,14 @@
       <c r="AP25" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY25" t="n">
+        <v>483651.19</v>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3526,6 +4139,24 @@
       <c r="AD26" t="n">
         <v>0.9831</v>
       </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI26" t="n">
+        <v>16492.12</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3534,6 +4165,14 @@
       <c r="AP26" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY26" t="n">
+        <v>276978.83</v>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3618,6 +4257,24 @@
       <c r="AD27" t="n">
         <v>0.9085</v>
       </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI27" t="n">
+        <v>16217.01</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3626,6 +4283,14 @@
       <c r="AP27" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY27" t="n">
+        <v>291813.17</v>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3710,6 +4375,24 @@
       <c r="AD28" t="n">
         <v>0.8095</v>
       </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI28" t="n">
+        <v>9797.68</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3718,6 +4401,14 @@
       <c r="AP28" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY28" t="n">
+        <v>405979.35</v>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3802,6 +4493,24 @@
       <c r="AD29" t="n">
         <v>0.8602</v>
       </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI29" t="n">
+        <v>5785.99</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3810,6 +4519,14 @@
       <c r="AP29" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY29" t="n">
+        <v>142453.77</v>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3894,6 +4611,24 @@
       <c r="AD30" t="n">
         <v>1.0325</v>
       </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI30" t="n">
+        <v>30416.67</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3902,6 +4637,14 @@
       <c r="AP30" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY30" t="n">
+        <v>181257.41</v>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -3986,6 +4729,24 @@
       <c r="AD31" t="n">
         <v>0.8529</v>
       </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI31" t="n">
+        <v>7683.11</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -3994,6 +4755,14 @@
       <c r="AP31" t="inlineStr">
         <is>
           <t>freshwatch_store</t>
+        </is>
+      </c>
+      <c r="AY31" t="n">
+        <v>133112.02</v>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -4075,6 +4844,24 @@
       <c r="AC32" t="n">
         <v>4.7537</v>
       </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>N/A-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="AI32" t="n">
+        <v>770626.17</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>ABSTAIN-STRUCTURAL</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -4083,6 +4870,14 @@
       <c r="AP32" t="inlineStr">
         <is>
           <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AY32" t="n">
+        <v>2304652.76</v>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>bybit</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="10" min="1" max="2"/>
@@ -4584,10 +5379,6 @@
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="n"/>
     </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4599,7 +5390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -4620,7 +5411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -4641,7 +5432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -4662,7 +5453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
